--- a/Project-14 ---/Data/data.xlsx
+++ b/Project-14 ---/Data/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-14 ---\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2FFE82-E972-4C82-9BB6-FB8B600C1317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCB913E-B5E8-4904-89E3-40D254A6E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7485" yWindow="1200" windowWidth="16335" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Input" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Codebook!$A$1:$D$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Input'!$A$1:$BU$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Input'!$A$3:$BU$106</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1923,6 +1923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:BU499"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6229,7 +6230,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>393</v>
@@ -11630,7 +11631,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="2" t="s">
         <v>416</v>
@@ -13658,7 +13659,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2" t="s">
         <v>415</v>
@@ -15455,7 +15456,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="68" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="2" t="s">
         <v>414</v>
@@ -16679,7 +16680,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="74" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="2" t="s">
         <v>391</v>
@@ -17694,7 +17695,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="79" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="2" t="s">
         <v>397</v>
@@ -17893,7 +17894,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="80" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="2" t="s">
         <v>370</v>
@@ -18094,7 +18095,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="81" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="2" t="s">
         <v>404</v>
@@ -18293,7 +18294,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="82" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="2" t="s">
         <v>371</v>
@@ -18494,7 +18495,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="83" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="2" t="s">
         <v>334</v>
@@ -18693,7 +18694,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="84" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="2" t="s">
         <v>399</v>
@@ -18896,7 +18897,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="85" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2" t="s">
         <v>383</v>
@@ -19105,7 +19106,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="86" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2" t="s">
         <v>382</v>
@@ -19310,7 +19311,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="87" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2" t="s">
         <v>393</v>
@@ -19509,7 +19510,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="88" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2" t="s">
         <v>400</v>
@@ -19710,7 +19711,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="89" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="2" t="s">
         <v>370</v>
@@ -20112,7 +20113,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="91" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2" t="s">
         <v>407</v>
@@ -20313,7 +20314,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="92" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2" t="s">
         <v>413</v>
@@ -20512,7 +20513,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="93" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2" t="s">
         <v>379</v>
@@ -20711,7 +20712,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="94" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2" t="s">
         <v>381</v>
@@ -20922,7 +20923,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="95" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2" t="s">
         <v>390</v>
@@ -21133,7 +21134,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="96" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2" t="s">
         <v>413</v>
@@ -21348,7 +21349,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="97" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="2" t="s">
         <v>341</v>
@@ -21549,7 +21550,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="98" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2" t="s">
         <v>380</v>
@@ -21750,7 +21751,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="99" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="2" t="s">
         <v>406</v>
@@ -21951,7 +21952,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="100" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>398</v>
       </c>
@@ -52838,7 +52839,13 @@
       <c r="BU499" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BU3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:BU106" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="71">
+      <filters>
+        <filter val="Survivor"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Project-14 ---/Data/data.xlsx
+++ b/Project-14 ---/Data/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-14 ---\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCB913E-B5E8-4904-89E3-40D254A6E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B629021D-8CDD-484B-965F-AAF5D3019761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,25 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Codebook!$A$1:$D$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Input'!$A$3:$BU$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Input'!$A$3:$BU$105</definedName>
   </definedNames>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="493">
   <si>
     <t>study_id</t>
   </si>
@@ -844,9 +855,6 @@
     <t xml:space="preserve">Cortical echogenicity increased </t>
   </si>
   <si>
-    <t xml:space="preserve">CT brain : Deep white matter ischaemic change b </t>
-  </si>
-  <si>
     <t xml:space="preserve">both kidneys are swollen </t>
   </si>
   <si>
@@ -1249,9 +1257,6 @@
     <t>9.4.25</t>
   </si>
   <si>
-    <t>2.10.25</t>
-  </si>
-  <si>
     <t>6.8.25</t>
   </si>
   <si>
@@ -1469,9 +1474,6 @@
   </si>
   <si>
     <t>26.3.25</t>
-  </si>
-  <si>
-    <t>8.10.25</t>
   </si>
   <si>
     <t>13.8.25</t>
@@ -1923,8 +1925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:BU499"/>
+  <dimension ref="A1:BU498"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2629,7 +2630,7 @@
     <row r="4" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -2646,11 +2647,17 @@
       <c r="G4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1" t="s">
         <v>233</v>
@@ -2692,7 +2699,7 @@
         <v>2</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB4" s="1">
         <v>511</v>
@@ -2822,13 +2829,13 @@
         <v>237</v>
       </c>
       <c r="BU4" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C5" s="1">
         <v>30</v>
@@ -2845,11 +2852,17 @@
       <c r="G5" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1" t="s">
         <v>233</v>
@@ -3021,13 +3034,13 @@
         <v>237</v>
       </c>
       <c r="BU5" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C6" s="1">
         <v>30</v>
@@ -3049,8 +3062,12 @@
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
         <v>242</v>
@@ -3211,7 +3228,7 @@
         <v>206</v>
       </c>
       <c r="BP6" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BQ6" s="1" t="s">
         <v>206</v>
@@ -3224,13 +3241,13 @@
         <v>237</v>
       </c>
       <c r="BU6" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -3239,7 +3256,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F7" s="1">
         <v>1748532263</v>
@@ -3255,7 +3272,9 @@
       <c r="K7" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
         <v>185</v>
@@ -3429,15 +3448,15 @@
         <v>237</v>
       </c>
       <c r="BU7" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -3451,12 +3470,20 @@
       <c r="F8" s="1">
         <v>17773910137</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1" t="s">
         <v>233</v>
@@ -3623,20 +3650,20 @@
         <v>235</v>
       </c>
       <c r="BR8" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS8" s="1"/>
       <c r="BT8" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU8" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C9" s="1">
         <v>29</v>
@@ -3645,7 +3672,7 @@
         <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F9" s="1">
         <v>1750697130</v>
@@ -3658,8 +3685,12 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
         <v>253</v>
@@ -3701,7 +3732,7 @@
         <v>2</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB9" s="1">
         <v>300</v>
@@ -3779,7 +3810,7 @@
         <v>2.33</v>
       </c>
       <c r="BA9" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BB9" s="1">
         <v>1</v>
@@ -3820,28 +3851,28 @@
         <v>206</v>
       </c>
       <c r="BP9" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ9" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR9" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="BS9" s="1"/>
       <c r="BT9" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU9" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
@@ -3850,17 +3881,25 @@
         <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F10" s="1">
         <v>1718619765</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
         <v>253</v>
@@ -4021,28 +4060,28 @@
         <v>206</v>
       </c>
       <c r="BP10" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ10" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR10" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BS10" s="1"/>
       <c r="BT10" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU10" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
@@ -4051,7 +4090,7 @@
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F11" s="1">
         <v>1752083265</v>
@@ -4059,11 +4098,17 @@
       <c r="G11" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
         <v>253</v>
@@ -4222,7 +4267,7 @@
         <v>206</v>
       </c>
       <c r="BP11" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ11" s="1" t="s">
         <v>235</v>
@@ -4235,15 +4280,15 @@
         <v>237</v>
       </c>
       <c r="BU11" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C12" s="1">
         <v>30</v>
@@ -4260,11 +4305,17 @@
       <c r="G12" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1" t="s">
         <v>253</v>
@@ -4423,26 +4474,26 @@
         <v>206</v>
       </c>
       <c r="BP12" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ12" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR12" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS12" s="1"/>
       <c r="BT12" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU12" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
@@ -4451,7 +4502,7 @@
         <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F13" s="1">
         <v>1928975533</v>
@@ -4459,11 +4510,17 @@
       <c r="G13" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
         <v>253</v>
@@ -4622,26 +4679,26 @@
         <v>206</v>
       </c>
       <c r="BP13" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ13" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR13" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BS13" s="1"/>
       <c r="BT13" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU13" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C14" s="1">
         <v>30</v>
@@ -4658,11 +4715,17 @@
       <c r="G14" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="K14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1" t="s">
         <v>253</v>
@@ -4702,7 +4765,7 @@
         <v>3</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB14" s="1">
         <v>300</v>
@@ -4821,26 +4884,26 @@
         <v>206</v>
       </c>
       <c r="BP14" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ14" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR14" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS14" s="1"/>
       <c r="BT14" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU14" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="1">
         <v>30</v>
@@ -4857,11 +4920,17 @@
       <c r="G15" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
         <v>253</v>
@@ -5022,26 +5091,26 @@
         <v>206</v>
       </c>
       <c r="BP15" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ15" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR15" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS15" s="1"/>
       <c r="BT15" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU15" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -5055,12 +5124,20 @@
       <c r="F16" s="1">
         <v>1762974840</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1" t="s">
         <v>253</v>
@@ -5219,26 +5296,26 @@
         <v>206</v>
       </c>
       <c r="BP16" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ16" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR16" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS16" s="1"/>
       <c r="BT16" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU16" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C17" s="1">
         <v>30</v>
@@ -5255,11 +5332,17 @@
       <c r="G17" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
         <v>253</v>
@@ -5418,26 +5501,26 @@
         <v>206</v>
       </c>
       <c r="BP17" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ17" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR17" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS17" s="1"/>
       <c r="BT17" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU17" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C18" s="1">
         <v>2</v>
@@ -5454,11 +5537,17 @@
       <c r="G18" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
         <v>253</v>
@@ -5617,26 +5706,26 @@
         <v>206</v>
       </c>
       <c r="BP18" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ18" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR18" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS18" s="1"/>
       <c r="BT18" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU18" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C19" s="1">
         <v>30</v>
@@ -5650,12 +5739,20 @@
       <c r="F19" s="1">
         <v>1744756203</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1" t="s">
         <v>253</v>
@@ -5814,26 +5911,26 @@
         <v>206</v>
       </c>
       <c r="BP19" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BQ19" s="1" t="s">
         <v>235</v>
       </c>
       <c r="BR19" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS19" s="1"/>
       <c r="BT19" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU19" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C20" s="1">
         <v>2</v>
@@ -5850,11 +5947,17 @@
       <c r="G20" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1" t="s">
         <v>233</v>
@@ -6019,20 +6122,20 @@
         <v>235</v>
       </c>
       <c r="BR20" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS20" s="1"/>
       <c r="BT20" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU20" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C21" s="1">
         <v>2</v>
@@ -6049,11 +6152,17 @@
       <c r="G21" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H21" s="1"/>
+      <c r="H21" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1" t="s">
         <v>233</v>
@@ -6207,7 +6316,7 @@
         <v>223</v>
       </c>
       <c r="BM21" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BN21" s="1"/>
       <c r="BO21" s="1" t="s">
@@ -6220,20 +6329,20 @@
         <v>235</v>
       </c>
       <c r="BR21" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="BS21" s="1"/>
       <c r="BT21" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU21" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="22" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C22" s="1">
         <v>30</v>
@@ -6258,7 +6367,9 @@
       <c r="K22" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="s">
         <v>199</v>
@@ -6432,15 +6543,15 @@
         <v>209</v>
       </c>
       <c r="BU22" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -6454,11 +6565,17 @@
       <c r="F23" s="1">
         <v>1737001344</v>
       </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="L23" s="1" t="s">
         <v>241</v>
       </c>
@@ -6470,7 +6587,7 @@
         <v>184</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q23" s="1">
         <v>28</v>
@@ -6581,7 +6698,7 @@
         <v>3.28</v>
       </c>
       <c r="BA23" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB23" s="1">
         <v>0.6</v>
@@ -6622,28 +6739,28 @@
         <v>206</v>
       </c>
       <c r="BP23" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ23" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR23" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS23" s="1"/>
       <c r="BT23" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU23" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="C24" s="1">
         <v>29</v>
@@ -6658,12 +6775,16 @@
         <v>17414549616</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="L24" s="1" t="s">
         <v>241</v>
       </c>
@@ -6675,7 +6796,7 @@
         <v>184</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q24" s="1">
         <v>24</v>
@@ -6827,28 +6948,28 @@
         <v>206</v>
       </c>
       <c r="BP24" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BQ24" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR24" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS24" s="1"/>
       <c r="BT24" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU24" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C25" s="1">
         <v>29</v>
@@ -6857,17 +6978,25 @@
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F25" s="1">
         <v>1719204361</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1" t="s">
         <v>247</v>
@@ -6909,7 +7038,7 @@
         <v>1</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB25" s="1">
         <v>310</v>
@@ -7028,7 +7157,7 @@
         <v>206</v>
       </c>
       <c r="BP25" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BQ25" s="1" t="s">
         <v>206</v>
@@ -7041,15 +7170,15 @@
         <v>237</v>
       </c>
       <c r="BU25" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="C26" s="1">
         <v>3</v>
@@ -7058,17 +7187,25 @@
         <v>62</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F26" s="1">
         <v>1717534529</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
         <v>242</v>
@@ -7077,7 +7214,7 @@
         <v>184</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q26" s="1">
         <v>26</v>
@@ -7110,7 +7247,7 @@
         <v>1</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB26" s="1">
         <v>277</v>
@@ -7229,7 +7366,7 @@
         <v>206</v>
       </c>
       <c r="BP26" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="BQ26" s="1"/>
       <c r="BR26" s="1" t="s">
@@ -7240,15 +7377,15 @@
         <v>237</v>
       </c>
       <c r="BU26" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="C27" s="1">
         <v>29</v>
@@ -7257,17 +7394,25 @@
         <v>80</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F27" s="1">
         <v>1730822897</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1" t="s">
         <v>242</v>
@@ -7276,7 +7421,7 @@
         <v>184</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q27" s="1">
         <v>25</v>
@@ -7309,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB27" s="1">
         <v>300</v>
@@ -7428,7 +7573,7 @@
         <v>206</v>
       </c>
       <c r="BP27" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ27" s="1"/>
       <c r="BR27" s="1" t="s">
@@ -7439,15 +7584,15 @@
         <v>237</v>
       </c>
       <c r="BU27" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="C28" s="1">
         <v>3</v>
@@ -7456,16 +7601,22 @@
         <v>65</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F28" s="1">
         <v>1313323078</v>
       </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="K28" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="L28" s="1" t="s">
         <v>211</v>
       </c>
@@ -7477,7 +7628,7 @@
         <v>184</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q28" s="1">
         <v>32</v>
@@ -7510,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB28" s="1">
         <v>259</v>
@@ -7629,7 +7780,7 @@
         <v>206</v>
       </c>
       <c r="BP28" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="BQ28" s="1"/>
       <c r="BR28" s="1" t="s">
@@ -7640,15 +7791,15 @@
         <v>237</v>
       </c>
       <c r="BU28" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C29" s="1">
         <v>29</v>
@@ -7657,17 +7808,25 @@
         <v>50</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F29" s="1">
         <v>1820546919</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1" t="s">
         <v>242</v>
@@ -7676,7 +7835,7 @@
         <v>184</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q29" s="1">
         <v>24</v>
@@ -7709,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB29" s="1">
         <v>277</v>
@@ -7828,26 +7987,26 @@
         <v>206</v>
       </c>
       <c r="BP29" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ29" s="1"/>
       <c r="BR29" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS29" s="1"/>
       <c r="BT29" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU29" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C30" s="1">
         <v>30</v>
@@ -7861,12 +8020,20 @@
       <c r="F30" s="1">
         <v>1302523166</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1" t="s">
         <v>242</v>
@@ -7875,7 +8042,7 @@
         <v>184</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q30" s="1">
         <v>28</v>
@@ -7908,7 +8075,7 @@
         <v>1</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB30" s="1">
         <v>277</v>
@@ -8027,7 +8194,7 @@
         <v>206</v>
       </c>
       <c r="BP30" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ30" s="1" t="s">
         <v>206</v>
@@ -8040,15 +8207,15 @@
         <v>237</v>
       </c>
       <c r="BU30" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="C31" s="1">
         <v>3</v>
@@ -8057,17 +8224,25 @@
         <v>40</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F31" s="1">
         <v>1737283966</v>
       </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1" t="s">
         <v>242</v>
@@ -8076,7 +8251,7 @@
         <v>184</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q31" s="1">
         <v>31</v>
@@ -8109,7 +8284,7 @@
         <v>2</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB31" s="1">
         <v>259</v>
@@ -8228,7 +8403,7 @@
         <v>206</v>
       </c>
       <c r="BP31" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ31" s="1" t="s">
         <v>206</v>
@@ -8241,13 +8416,13 @@
         <v>237</v>
       </c>
       <c r="BU31" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
@@ -8256,17 +8431,25 @@
         <v>61</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F32" s="1">
         <v>1723149130</v>
       </c>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1" t="s">
         <v>242</v>
@@ -8275,7 +8458,7 @@
         <v>184</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q32" s="1">
         <v>20</v>
@@ -8308,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB32" s="1">
         <v>277</v>
@@ -8427,7 +8610,7 @@
         <v>206</v>
       </c>
       <c r="BP32" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ32" s="1" t="s">
         <v>206</v>
@@ -8440,13 +8623,13 @@
         <v>237</v>
       </c>
       <c r="BU32" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="33" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C33" s="1">
         <v>3</v>
@@ -8455,17 +8638,25 @@
         <v>65</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F33" s="1">
         <v>1719416032</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1" t="s">
         <v>242</v>
@@ -8474,7 +8665,7 @@
         <v>184</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q33" s="1">
         <v>23</v>
@@ -8507,7 +8698,7 @@
         <v>2</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB33" s="1">
         <v>232</v>
@@ -8626,7 +8817,7 @@
         <v>206</v>
       </c>
       <c r="BP33" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ33" s="1" t="s">
         <v>206</v>
@@ -8639,13 +8830,13 @@
         <v>237</v>
       </c>
       <c r="BU33" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C34" s="1">
         <v>30</v>
@@ -8659,12 +8850,20 @@
       <c r="F34" s="1">
         <v>1771253410</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
         <v>242</v>
@@ -8673,7 +8872,7 @@
         <v>184</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q34" s="1">
         <v>31</v>
@@ -8706,7 +8905,7 @@
         <v>2</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB34" s="1">
         <v>244</v>
@@ -8825,7 +9024,7 @@
         <v>206</v>
       </c>
       <c r="BP34" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BQ34" s="1" t="s">
         <v>206</v>
@@ -8838,13 +9037,13 @@
         <v>237</v>
       </c>
       <c r="BU34" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
@@ -8853,17 +9052,25 @@
         <v>68</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F35" s="1">
         <v>1924652940</v>
       </c>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="K35" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1" t="s">
         <v>242</v>
@@ -8872,7 +9079,7 @@
         <v>184</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q35" s="1">
         <v>22</v>
@@ -8905,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="AA35" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB35" s="1">
         <v>443</v>
@@ -9024,7 +9231,7 @@
         <v>206</v>
       </c>
       <c r="BP35" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ35" s="1" t="s">
         <v>206</v>
@@ -9037,13 +9244,13 @@
         <v>237</v>
       </c>
       <c r="BU35" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C36" s="1">
         <v>3</v>
@@ -9052,17 +9259,25 @@
         <v>55</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F36" s="1">
         <v>1889639196</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1" t="s">
         <v>242</v>
@@ -9071,7 +9286,7 @@
         <v>184</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q36" s="1">
         <v>22</v>
@@ -9104,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="AA36" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB36" s="1">
         <v>277</v>
@@ -9223,7 +9438,7 @@
         <v>206</v>
       </c>
       <c r="BP36" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ36" s="1" t="s">
         <v>206</v>
@@ -9236,13 +9451,13 @@
         <v>237</v>
       </c>
       <c r="BU36" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
@@ -9251,17 +9466,25 @@
         <v>55</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F37" s="1">
         <v>1615472612</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1" t="s">
         <v>242</v>
@@ -9270,7 +9493,7 @@
         <v>184</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q37" s="1">
         <v>32</v>
@@ -9303,7 +9526,7 @@
         <v>2</v>
       </c>
       <c r="AA37" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB37" s="1">
         <v>369</v>
@@ -9422,7 +9645,7 @@
         <v>206</v>
       </c>
       <c r="BP37" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ37" s="1" t="s">
         <v>206</v>
@@ -9435,13 +9658,13 @@
         <v>237</v>
       </c>
       <c r="BU37" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C38" s="1">
         <v>29</v>
@@ -9450,17 +9673,25 @@
         <v>63</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F38" s="1">
         <v>1733140848</v>
       </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1" t="s">
         <v>242</v>
@@ -9469,7 +9700,7 @@
         <v>184</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q38" s="1">
         <v>26</v>
@@ -9502,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AB38" s="1">
         <v>277</v>
@@ -9621,7 +9852,7 @@
         <v>206</v>
       </c>
       <c r="BP38" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ38" s="1" t="s">
         <v>206</v>
@@ -9634,13 +9865,13 @@
         <v>237</v>
       </c>
       <c r="BU38" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
@@ -9649,7 +9880,7 @@
         <v>60</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F39" s="1">
         <v>164446724</v>
@@ -9657,11 +9888,17 @@
       <c r="G39" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1" t="s">
         <v>172</v>
@@ -9670,7 +9907,7 @@
         <v>184</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q39" s="1">
         <v>24</v>
@@ -9822,26 +10059,26 @@
         <v>235</v>
       </c>
       <c r="BP39" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ39" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR39" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BS39" s="1"/>
       <c r="BT39" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU39" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C40" s="1">
         <v>30</v>
@@ -9855,12 +10092,20 @@
       <c r="F40" s="1">
         <v>1751479435</v>
       </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="G40" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
         <v>172</v>
@@ -9869,7 +10114,7 @@
         <v>184</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q40" s="1">
         <v>23</v>
@@ -10021,26 +10266,26 @@
         <v>235</v>
       </c>
       <c r="BP40" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ40" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR40" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS40" s="1"/>
       <c r="BT40" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU40" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C41" s="1">
         <v>2</v>
@@ -10054,12 +10299,20 @@
       <c r="F41" s="1">
         <v>1764214243</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
         <v>172</v>
@@ -10068,7 +10321,7 @@
         <v>184</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q41" s="1">
         <v>24</v>
@@ -10220,26 +10473,26 @@
         <v>235</v>
       </c>
       <c r="BP41" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ41" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR41" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS41" s="1"/>
       <c r="BT41" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU41" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C42" s="1">
         <v>2</v>
@@ -10253,12 +10506,20 @@
       <c r="F42" s="1">
         <v>1750827781</v>
       </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
         <v>172</v>
@@ -10267,7 +10528,7 @@
         <v>184</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q42" s="1">
         <v>21</v>
@@ -10419,26 +10680,26 @@
         <v>235</v>
       </c>
       <c r="BP42" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ42" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR42" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BS42" s="1"/>
       <c r="BT42" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU42" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="43" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C43" s="1">
         <v>30</v>
@@ -10452,12 +10713,20 @@
       <c r="F43" s="1">
         <v>1786990243</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="K43" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1" t="s">
         <v>172</v>
@@ -10466,7 +10735,7 @@
         <v>184</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q43" s="1">
         <v>24</v>
@@ -10618,26 +10887,26 @@
         <v>235</v>
       </c>
       <c r="BP43" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="BQ43" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR43" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS43" s="1"/>
       <c r="BT43" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU43" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
@@ -10646,17 +10915,25 @@
         <v>35</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F44" s="1">
         <v>1793549973</v>
       </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+      <c r="G44" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
         <v>172</v>
@@ -10665,7 +10942,7 @@
         <v>184</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q44" s="1">
         <v>21</v>
@@ -10817,26 +11094,26 @@
         <v>235</v>
       </c>
       <c r="BP44" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="BQ44" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR44" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS44" s="1"/>
       <c r="BT44" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU44" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="45" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C45" s="1">
         <v>3</v>
@@ -10845,17 +11122,25 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F45" s="1">
         <v>1731655159</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
+      <c r="G45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
+      <c r="K45" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
         <v>172</v>
@@ -10864,7 +11149,7 @@
         <v>257</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q45" s="1">
         <v>31</v>
@@ -10975,7 +11260,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="BA45" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB45" s="1">
         <v>1.3</v>
@@ -11016,7 +11301,7 @@
         <v>235</v>
       </c>
       <c r="BP45" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="BQ45" s="1" t="s">
         <v>206</v>
@@ -11029,15 +11314,15 @@
         <v>237</v>
       </c>
       <c r="BU45" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
@@ -11046,20 +11331,28 @@
         <v>65</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F46" s="1">
         <v>1795697129</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
+      <c r="K46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>241</v>
@@ -11223,20 +11516,20 @@
         <v>235</v>
       </c>
       <c r="BR46" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS46" s="1"/>
       <c r="BT46" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU46" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C47" s="1">
         <v>3</v>
@@ -11245,17 +11538,25 @@
         <v>72</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F47" s="1">
         <v>1734484744</v>
       </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+      <c r="G47" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
+      <c r="K47" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
         <v>247</v>
@@ -11422,20 +11723,20 @@
         <v>235</v>
       </c>
       <c r="BR47" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS47" s="1"/>
       <c r="BT47" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU47" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C48" s="1">
         <v>2</v>
@@ -11452,11 +11753,17 @@
       <c r="G48" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H48" s="1"/>
+      <c r="H48" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
+      <c r="K48" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
         <v>247</v>
@@ -11465,7 +11772,7 @@
         <v>210</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q48" s="1">
         <v>18</v>
@@ -11621,20 +11928,20 @@
         <v>235</v>
       </c>
       <c r="BR48" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BS48" s="1"/>
       <c r="BT48" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU48" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="49" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="49" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
@@ -11643,17 +11950,25 @@
         <v>37</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F49" s="1">
         <v>1729294846</v>
       </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
+      <c r="K49" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
         <v>176</v>
@@ -11831,13 +12146,13 @@
         <v>219</v>
       </c>
       <c r="BU49" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
@@ -11846,7 +12161,7 @@
         <v>46</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F50" s="1">
         <v>1713730822</v>
@@ -11854,11 +12169,17 @@
       <c r="G50" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H50" s="1"/>
+      <c r="H50" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="K50" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1" t="s">
         <v>233</v>
@@ -11867,7 +12188,7 @@
         <v>202</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q50" s="1">
         <v>18</v>
@@ -12014,7 +12335,7 @@
         <v>223</v>
       </c>
       <c r="BM50" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN50" s="1"/>
       <c r="BO50" s="1" t="s">
@@ -12027,22 +12348,22 @@
         <v>221</v>
       </c>
       <c r="BR50" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BS50" s="1"/>
       <c r="BT50" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU50" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C51" s="1">
         <v>2</v>
@@ -12056,12 +12377,20 @@
       <c r="F51" s="1">
         <v>1737717732</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
+      <c r="K51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1" t="s">
         <v>233</v>
@@ -12217,7 +12546,7 @@
         <v>223</v>
       </c>
       <c r="BM51" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN51" s="1"/>
       <c r="BO51" s="1" t="s">
@@ -12230,20 +12559,20 @@
         <v>221</v>
       </c>
       <c r="BR51" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BS51" s="1"/>
       <c r="BT51" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU51" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="52" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
@@ -12252,7 +12581,7 @@
         <v>51</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F52" s="1">
         <v>1992489232</v>
@@ -12260,11 +12589,17 @@
       <c r="G52" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="K52" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
         <v>233</v>
@@ -12273,7 +12608,7 @@
         <v>202</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q52" s="1">
         <v>18</v>
@@ -12420,7 +12755,7 @@
         <v>223</v>
       </c>
       <c r="BM52" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BN52" s="1"/>
       <c r="BO52" s="1" t="s">
@@ -12433,20 +12768,20 @@
         <v>221</v>
       </c>
       <c r="BR52" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="BS52" s="1"/>
       <c r="BT52" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU52" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C53" s="1">
         <v>2</v>
@@ -12460,12 +12795,20 @@
       <c r="F53" s="1">
         <v>179890578</v>
       </c>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="G53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
+      <c r="K53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
         <v>233</v>
@@ -12474,7 +12817,7 @@
         <v>210</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q53" s="1">
         <v>21</v>
@@ -12621,7 +12964,7 @@
         <v>223</v>
       </c>
       <c r="BM53" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BN53" s="1"/>
       <c r="BO53" s="1" t="s">
@@ -12634,20 +12977,20 @@
         <v>221</v>
       </c>
       <c r="BR53" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="BS53" s="1"/>
       <c r="BT53" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU53" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C54" s="1">
         <v>3</v>
@@ -12656,7 +12999,7 @@
         <v>74</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F54" s="1">
         <v>1723488712</v>
@@ -12664,11 +13007,17 @@
       <c r="G54" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="H54" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="K54" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1" t="s">
         <v>233</v>
@@ -12824,7 +13173,7 @@
         <v>223</v>
       </c>
       <c r="BM54" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BN54" s="1"/>
       <c r="BO54" s="1" t="s">
@@ -12837,20 +13186,20 @@
         <v>221</v>
       </c>
       <c r="BR54" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BS54" s="1"/>
       <c r="BT54" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU54" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
@@ -12859,7 +13208,7 @@
         <v>40</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F55" s="1">
         <v>1716304046</v>
@@ -12867,20 +13216,26 @@
       <c r="G55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="H55" s="1"/>
+      <c r="H55" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
+      <c r="K55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>202</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q55" s="1">
         <v>20</v>
@@ -13027,7 +13382,7 @@
         <v>223</v>
       </c>
       <c r="BM55" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN55" s="1"/>
       <c r="BO55" s="1" t="s">
@@ -13040,20 +13395,20 @@
         <v>221</v>
       </c>
       <c r="BR55" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BS55" s="1"/>
       <c r="BT55" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU55" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
@@ -13062,7 +13417,7 @@
         <v>53</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F56" s="1">
         <v>1331997809</v>
@@ -13070,20 +13425,26 @@
       <c r="G56" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H56" s="1"/>
+      <c r="H56" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
+      <c r="K56" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>202</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q56" s="1">
         <v>18</v>
@@ -13230,13 +13591,13 @@
         <v>223</v>
       </c>
       <c r="BM56" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN56" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="BO56" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="BO56" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="BP56" s="1" t="s">
         <v>207</v>
@@ -13252,13 +13613,13 @@
         <v>237</v>
       </c>
       <c r="BU56" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -13272,12 +13633,20 @@
       <c r="F57" s="1">
         <v>1767303222</v>
       </c>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="G57" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="K57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1" t="s">
         <v>233</v>
@@ -13433,7 +13802,7 @@
         <v>223</v>
       </c>
       <c r="BM57" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BN57" s="1" t="s">
         <v>217</v>
@@ -13448,20 +13817,20 @@
         <v>221</v>
       </c>
       <c r="BR57" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="BS57" s="1"/>
       <c r="BT57" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU57" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C58" s="1">
         <v>3</v>
@@ -13470,17 +13839,25 @@
         <v>30</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F58" s="1">
         <v>1332065061</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
+      <c r="G58" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
+      <c r="K58" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1" t="s">
         <v>262</v>
@@ -13649,20 +14026,20 @@
         <v>206</v>
       </c>
       <c r="BR58" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="BS58" s="1"/>
       <c r="BT58" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU58" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="59" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="59" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C59" s="1">
         <v>26</v>
@@ -13671,17 +14048,25 @@
         <v>26</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F59" s="1">
         <v>1738759837</v>
       </c>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="G59" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
+      <c r="K59" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1" t="s">
         <v>176</v>
@@ -13859,13 +14244,13 @@
         <v>229</v>
       </c>
       <c r="BU59" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="60" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C60" s="1">
         <v>29</v>
@@ -13874,17 +14259,25 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F60" s="1">
         <v>1737588357</v>
       </c>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="G60" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="K60" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1" t="s">
         <v>253</v>
@@ -14051,20 +14444,20 @@
         <v>206</v>
       </c>
       <c r="BR60" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BS60" s="1"/>
       <c r="BT60" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU60" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="61" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C61" s="1">
         <v>2</v>
@@ -14073,17 +14466,25 @@
         <v>55</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F61" s="1">
         <v>1719515158</v>
       </c>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
+      <c r="K61" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1" t="s">
         <v>233</v>
@@ -14248,20 +14649,20 @@
         <v>235</v>
       </c>
       <c r="BR61" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS61" s="1"/>
       <c r="BT61" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU61" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C62" s="1">
         <v>30</v>
@@ -14275,12 +14676,20 @@
       <c r="F62" s="1">
         <v>177641700</v>
       </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
+      <c r="G62" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="K62" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1" t="s">
         <v>233</v>
@@ -14445,20 +14854,20 @@
         <v>235</v>
       </c>
       <c r="BR62" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS62" s="1"/>
       <c r="BT62" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU62" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="63" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C63" s="1">
         <v>2</v>
@@ -14472,12 +14881,20 @@
       <c r="F63" s="1">
         <v>1962553029</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
+      <c r="K63" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1" t="s">
         <v>253</v>
@@ -14642,22 +15059,22 @@
         <v>235</v>
       </c>
       <c r="BR63" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS63" s="1"/>
       <c r="BT63" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU63" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C64" s="1">
         <v>29</v>
@@ -14666,7 +15083,7 @@
         <v>42</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F64" s="1">
         <v>1755145202</v>
@@ -14674,11 +15091,17 @@
       <c r="G64" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H64" s="1"/>
+      <c r="H64" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
+      <c r="K64" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1" t="s">
         <v>233</v>
@@ -14843,22 +15266,22 @@
         <v>235</v>
       </c>
       <c r="BR64" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS64" s="1"/>
       <c r="BT64" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU64" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C65" s="1">
         <v>29</v>
@@ -14867,7 +15290,7 @@
         <v>65</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F65" s="1">
         <v>1776969582</v>
@@ -14875,11 +15298,17 @@
       <c r="G65" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H65" s="1"/>
+      <c r="H65" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
+      <c r="K65" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1" t="s">
         <v>233</v>
@@ -15044,22 +15473,22 @@
         <v>235</v>
       </c>
       <c r="BR65" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="BS65" s="1"/>
       <c r="BT65" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU65" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="66" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
@@ -15068,17 +15497,25 @@
         <v>60</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F66" s="1">
         <v>1315161923</v>
       </c>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
+      <c r="G66" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
+      <c r="K66" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1" t="s">
         <v>233</v>
@@ -15245,22 +15682,22 @@
         <v>235</v>
       </c>
       <c r="BR66" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS66" s="1"/>
       <c r="BT66" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU66" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
@@ -15269,17 +15706,25 @@
         <v>50</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F67" s="1">
         <v>1780840495</v>
       </c>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
+      <c r="G67" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
+      <c r="K67" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1" t="s">
         <v>233</v>
@@ -15446,20 +15891,20 @@
         <v>235</v>
       </c>
       <c r="BR67" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS67" s="1"/>
       <c r="BT67" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU67" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="68" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="68" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C68" s="1">
         <v>3</v>
@@ -15467,16 +15912,26 @@
       <c r="D68" s="1">
         <v>65</v>
       </c>
-      <c r="E68" s="1"/>
+      <c r="E68" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="F68" s="1">
         <v>1780362912</v>
       </c>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
+      <c r="G68" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
+      <c r="K68" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1" t="s">
         <v>230</v>
@@ -15656,15 +16111,15 @@
         <v>219</v>
       </c>
       <c r="BU68" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="69" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="C69" s="1">
         <v>3</v>
@@ -15673,17 +16128,25 @@
         <v>41</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F69" s="1">
         <v>1867323076</v>
       </c>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
+      <c r="K69" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1" t="s">
         <v>253</v>
@@ -15725,7 +16188,7 @@
         <v>2</v>
       </c>
       <c r="AA69" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AB69" s="1">
         <v>400</v>
@@ -15803,7 +16266,7 @@
         <v>3.65</v>
       </c>
       <c r="BA69" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BB69" s="1">
         <v>2.2000000000000002</v>
@@ -15852,22 +16315,22 @@
         <v>221</v>
       </c>
       <c r="BR69" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS69" s="1"/>
       <c r="BT69" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU69" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C70" s="1">
         <v>30</v>
@@ -15884,11 +16347,17 @@
       <c r="G70" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H70" s="1"/>
+      <c r="H70" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
+      <c r="K70" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M70" s="1"/>
       <c r="N70" s="1" t="s">
         <v>253</v>
@@ -16057,24 +16526,24 @@
         <v>221</v>
       </c>
       <c r="BR70" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS70" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BT70" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU70" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="71" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C71" s="1">
         <v>2</v>
@@ -16088,12 +16557,20 @@
       <c r="F71" s="1">
         <v>1733068616</v>
       </c>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
+      <c r="G71" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
+      <c r="K71" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1" t="s">
         <v>233</v>
@@ -16260,24 +16737,24 @@
         <v>221</v>
       </c>
       <c r="BR71" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS71" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BT71" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU71" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="72" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C72" s="1">
         <v>3</v>
@@ -16286,7 +16763,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F72" s="1">
         <v>1945921456</v>
@@ -16294,11 +16771,17 @@
       <c r="G72" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H72" s="1"/>
+      <c r="H72" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
+      <c r="K72" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M72" s="1"/>
       <c r="N72" s="1" t="s">
         <v>233</v>
@@ -16465,24 +16948,24 @@
         <v>221</v>
       </c>
       <c r="BR72" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="BS72" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BT72" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU72" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C73" s="1">
         <v>30</v>
@@ -16496,12 +16979,20 @@
       <c r="F73" s="1">
         <v>1738382368</v>
       </c>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
+      <c r="G73" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M73" s="1"/>
       <c r="N73" s="1" t="s">
         <v>233</v>
@@ -16668,22 +17159,22 @@
         <v>221</v>
       </c>
       <c r="BR73" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BS73" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BT73" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BU73" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="74" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C74" s="1">
         <v>3</v>
@@ -16692,17 +17183,25 @@
         <v>22</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F74" s="1">
         <v>1771884054</v>
       </c>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
+      <c r="G74" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
+      <c r="K74" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M74" s="1"/>
       <c r="N74" s="1" t="s">
         <v>176</v>
@@ -16880,15 +17379,15 @@
         <v>219</v>
       </c>
       <c r="BU74" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C75" s="1">
         <v>19</v>
@@ -16902,12 +17401,20 @@
       <c r="F75" s="1">
         <v>17012109968</v>
       </c>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
+      <c r="K75" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M75" s="1"/>
       <c r="N75" s="1" t="s">
         <v>262</v>
@@ -17025,7 +17532,7 @@
         <v>3.4</v>
       </c>
       <c r="BA75" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB75" s="1">
         <v>1.1000000000000001</v>
@@ -17064,7 +17571,7 @@
         <v>246</v>
       </c>
       <c r="BN75" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="BO75" s="1" t="s">
         <v>221</v>
@@ -17076,22 +17583,22 @@
         <v>221</v>
       </c>
       <c r="BR75" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BS75" s="1"/>
       <c r="BT75" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU75" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="76" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C76" s="1">
         <v>30</v>
@@ -17105,12 +17612,20 @@
       <c r="F76" s="1">
         <v>1743224361</v>
       </c>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
+      <c r="G76" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
+      <c r="K76" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1" t="s">
         <v>262</v>
@@ -17230,7 +17745,7 @@
         <v>3.04</v>
       </c>
       <c r="BA76" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB76" s="1">
         <v>1.3</v>
@@ -17279,22 +17794,22 @@
         <v>221</v>
       </c>
       <c r="BR76" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="BS76" s="1"/>
       <c r="BT76" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU76" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="77" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C77" s="1">
         <v>2</v>
@@ -17308,12 +17823,20 @@
       <c r="F77" s="1">
         <v>1723818518</v>
       </c>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="G77" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
+      <c r="K77" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M77" s="1"/>
       <c r="N77" s="1" t="s">
         <v>262</v>
@@ -17433,7 +17956,7 @@
         <v>3.02</v>
       </c>
       <c r="BA77" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB77" s="1">
         <v>1.8</v>
@@ -17482,22 +18005,22 @@
         <v>221</v>
       </c>
       <c r="BR77" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BS77" s="1"/>
       <c r="BT77" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU77" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C78" s="1">
         <v>29</v>
@@ -17506,17 +18029,25 @@
         <v>40</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F78" s="1">
         <v>1814739585</v>
       </c>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
+      <c r="G78" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
+      <c r="K78" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M78" s="1"/>
       <c r="N78" s="1" t="s">
         <v>262</v>
@@ -17636,7 +18167,7 @@
         <v>2.93</v>
       </c>
       <c r="BA78" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BB78" s="1">
         <v>1.9</v>
@@ -17666,7 +18197,7 @@
         <v>221</v>
       </c>
       <c r="BK78" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="BL78" s="1" t="s">
         <v>223</v>
@@ -17685,20 +18216,20 @@
         <v>206</v>
       </c>
       <c r="BR78" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BS78" s="1"/>
       <c r="BT78" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU78" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="79" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
@@ -17712,21 +18243,29 @@
       <c r="F79" s="1">
         <v>1717886435</v>
       </c>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="G79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
+      <c r="K79" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M79" s="1"/>
       <c r="N79" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O79" s="1" t="s">
         <v>241</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q79" s="1">
         <v>27</v>
@@ -17837,7 +18376,7 @@
         <v>9.57</v>
       </c>
       <c r="BA79" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BB79" s="1">
         <v>2.2999999999999998</v>
@@ -17888,16 +18427,16 @@
       </c>
       <c r="BS79" s="1"/>
       <c r="BT79" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BU79" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="80" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="80" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C80" s="1">
         <v>3</v>
@@ -17906,19 +18445,25 @@
         <v>70</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F80" s="1">
         <v>1799360428</v>
       </c>
-      <c r="G80" s="1"/>
+      <c r="G80" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="H80" s="1" t="s">
         <v>241</v>
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
+      <c r="K80" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M80" s="1"/>
       <c r="N80" s="1" t="s">
         <v>233</v>
@@ -17960,7 +18505,7 @@
         <v>15</v>
       </c>
       <c r="AA80" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AB80" s="1">
         <v>277</v>
@@ -18092,13 +18637,13 @@
         <v>256</v>
       </c>
       <c r="BU80" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="81" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C81" s="1">
         <v>3</v>
@@ -18107,17 +18652,25 @@
         <v>35</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F81" s="1">
         <v>1937390824</v>
       </c>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
+      <c r="G81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="K81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M81" s="1"/>
       <c r="N81" s="1" t="s">
         <v>264</v>
@@ -18237,7 +18790,7 @@
         <v>16.14</v>
       </c>
       <c r="BA81" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="BB81" s="1">
         <v>3.7</v>
@@ -18291,13 +18844,13 @@
         <v>229</v>
       </c>
       <c r="BU81" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="82" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="82" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
@@ -18306,7 +18859,7 @@
         <v>55</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F82" s="1">
         <v>1724204867</v>
@@ -18314,11 +18867,17 @@
       <c r="G82" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H82" s="1"/>
+      <c r="H82" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
+      <c r="K82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M82" s="1"/>
       <c r="N82" s="1" t="s">
         <v>233</v>
@@ -18492,13 +19051,13 @@
         <v>209</v>
       </c>
       <c r="BU82" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="83" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="83" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C83" s="1">
         <v>30</v>
@@ -18507,20 +19066,28 @@
         <v>45</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F83" s="1">
         <v>1714882394</v>
       </c>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="G83" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
+      <c r="K83" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M83" s="1"/>
       <c r="N83" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O83" s="1" t="s">
         <v>184</v>
@@ -18678,7 +19245,7 @@
         <v>206</v>
       </c>
       <c r="BP83" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ83" s="1" t="s">
         <v>206</v>
@@ -18691,13 +19258,13 @@
         <v>229</v>
       </c>
       <c r="BU83" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="84" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="84" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C84" s="1">
         <v>30</v>
@@ -18706,7 +19273,7 @@
         <v>54</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F84" s="1">
         <v>1619872268</v>
@@ -18714,16 +19281,20 @@
       <c r="G84" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="H84" s="1"/>
+      <c r="H84" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L84" s="1"/>
       <c r="M84" s="1"/>
       <c r="N84" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>241</v>
@@ -18881,26 +19452,26 @@
         <v>206</v>
       </c>
       <c r="BP84" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BQ84" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR84" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="BS84" s="1"/>
       <c r="BT84" s="1" t="s">
         <v>209</v>
       </c>
       <c r="BU84" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="85" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="85" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C85" s="1">
         <v>29</v>
@@ -18909,7 +19480,7 @@
         <v>65</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F85" s="1">
         <v>1739149152</v>
@@ -18927,7 +19498,7 @@
         <v>211</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>211</v>
@@ -18937,7 +19508,7 @@
         <v>247</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1">
@@ -19090,7 +19661,7 @@
         <v>206</v>
       </c>
       <c r="BP85" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="BQ85" s="1" t="s">
         <v>206</v>
@@ -19103,13 +19674,13 @@
         <v>229</v>
       </c>
       <c r="BU85" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="86" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="86" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C86" s="1">
         <v>3</v>
@@ -19118,13 +19689,13 @@
         <v>60</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F86" s="1">
         <v>1945307667</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>202</v>
@@ -19134,16 +19705,18 @@
       <c r="K86" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L86" s="1"/>
+      <c r="L86" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M86" s="1"/>
       <c r="N86" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>184</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q86" s="1">
         <v>24</v>
@@ -19295,26 +19868,26 @@
         <v>206</v>
       </c>
       <c r="BP86" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BQ86" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR86" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BS86" s="1"/>
       <c r="BT86" s="1" t="s">
         <v>209</v>
       </c>
       <c r="BU86" s="2" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="87" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="87" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C87" s="1">
         <v>2</v>
@@ -19328,12 +19901,20 @@
       <c r="F87" s="1">
         <v>1704378913</v>
       </c>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
+      <c r="G87" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
+      <c r="K87" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L87" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M87" s="1"/>
       <c r="N87" s="1" t="s">
         <v>264</v>
@@ -19500,20 +20081,20 @@
         <v>206</v>
       </c>
       <c r="BR87" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BS87" s="1"/>
       <c r="BT87" s="1" t="s">
         <v>229</v>
       </c>
       <c r="BU87" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="88" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="88" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
@@ -19522,17 +20103,25 @@
         <v>73</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F88" s="1">
         <v>1859512290</v>
       </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
+      <c r="G88" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
+      <c r="K88" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M88" s="1"/>
       <c r="N88" s="1" t="s">
         <v>230</v>
@@ -19708,13 +20297,13 @@
         <v>218</v>
       </c>
       <c r="BU88" s="2" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="89" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C89" s="1">
         <v>30</v>
@@ -19731,11 +20320,17 @@
       <c r="G89" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H89" s="1"/>
+      <c r="H89" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
+      <c r="K89" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M89" s="1"/>
       <c r="N89" s="1" t="s">
         <v>253</v>
@@ -19911,7 +20506,7 @@
         <v>268</v>
       </c>
       <c r="BU89" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90" spans="1:73" x14ac:dyDescent="0.25">
@@ -19923,20 +20518,28 @@
         <v>3</v>
       </c>
       <c r="D90" s="1">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F90" s="1">
-        <v>1772668429</v>
-      </c>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
+        <v>1726426530</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
+      <c r="K90" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M90" s="1"/>
       <c r="N90" s="1" t="s">
         <v>253</v>
@@ -19948,61 +20551,61 @@
         <v>187</v>
       </c>
       <c r="Q90" s="1">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R90" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S90" s="1" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="T90" s="1">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="U90" s="1">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="V90" s="1">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="W90" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X90" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y90" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z90" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA90" s="1" t="s">
         <v>260</v>
       </c>
       <c r="AB90" s="1">
-        <v>345</v>
+        <v>244</v>
       </c>
       <c r="AC90" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD90" s="1">
-        <v>149000</v>
+        <v>168000</v>
       </c>
       <c r="AE90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF90" s="1">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="AG90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH90" s="1">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="AI90" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ90" s="1">
         <v>14</v>
@@ -20011,83 +20614,83 @@
         <v>1</v>
       </c>
       <c r="AL90" s="1">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AM90" s="1">
         <v>2</v>
       </c>
       <c r="AN90" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO90" s="1">
-        <v>9.5</v>
+        <v>10.47</v>
       </c>
       <c r="AP90" s="1">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AQ90" s="1">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="AR90" s="1">
-        <v>9.81</v>
+        <v>8.7799999999999994</v>
       </c>
       <c r="AS90" s="1">
-        <v>9.42</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="AT90" s="1">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="AU90" s="1">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="AV90" s="1">
-        <v>6.98</v>
+        <v>8.76</v>
       </c>
       <c r="AW90" s="1">
-        <v>10.18</v>
+        <v>10.11</v>
       </c>
       <c r="AX90" s="1">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="AY90" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AZ90" s="1">
-        <v>9.19</v>
+        <v>10.196</v>
       </c>
       <c r="BA90" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB90" s="1">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BC90" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BD90" s="1">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="BE90" s="1">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BF90" s="1">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="BG90" s="1">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="BH90" s="1">
-        <v>8.1999999999999993</v>
+        <v>12.5</v>
       </c>
       <c r="BI90" s="1">
-        <v>0.5</v>
+        <v>3.41</v>
       </c>
       <c r="BJ90" s="1" t="s">
         <v>203</v>
       </c>
       <c r="BK90" s="1"/>
       <c r="BL90" s="1" t="s">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="BM90" s="1" t="s">
         <v>213</v>
@@ -20103,192 +20706,198 @@
         <v>206</v>
       </c>
       <c r="BR90" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="BS90" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="BT90" s="1"/>
+      <c r="BS90" s="1"/>
+      <c r="BT90" s="1" t="s">
+        <v>268</v>
+      </c>
       <c r="BU90" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="91" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="91" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C91" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="1">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>343</v>
+        <v>165</v>
       </c>
       <c r="F91" s="1">
-        <v>1726426530</v>
+        <v>1937117349</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H91" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
+      <c r="K91" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M91" s="1"/>
       <c r="N91" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="O91" s="1" t="s">
         <v>186</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="Q91" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R91" s="1">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="S91" s="1" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="T91" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U91" s="1">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="V91" s="1">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="W91" s="1">
+        <v>15</v>
+      </c>
+      <c r="X91" s="1">
+        <v>9</v>
+      </c>
+      <c r="Y91" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z91" s="1">
         <v>13</v>
       </c>
-      <c r="X91" s="1">
-        <v>16</v>
-      </c>
-      <c r="Y91" s="1">
-        <v>16</v>
-      </c>
-      <c r="Z91" s="1">
-        <v>18</v>
-      </c>
       <c r="AA91" s="1" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="AB91" s="1">
-        <v>244</v>
+        <v>443</v>
       </c>
       <c r="AC91" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD91" s="1">
-        <v>168000</v>
+        <v>211000</v>
       </c>
       <c r="AE91" s="1">
         <v>0</v>
       </c>
       <c r="AF91" s="1">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="AG91" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH91" s="1">
+        <v>93</v>
+      </c>
+      <c r="AI91" s="1">
         <v>0</v>
       </c>
-      <c r="AH91" s="1">
-        <v>60</v>
-      </c>
-      <c r="AI91" s="1">
-        <v>3</v>
-      </c>
       <c r="AJ91" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL91" s="1">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AM91" s="1">
         <v>2</v>
       </c>
       <c r="AN91" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO91" s="1">
-        <v>10.47</v>
+        <v>9.56</v>
       </c>
       <c r="AP91" s="1">
-        <v>0.71</v>
+        <v>0.42</v>
       </c>
       <c r="AQ91" s="1">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="AR91" s="1">
-        <v>8.7799999999999994</v>
+        <v>10.78</v>
       </c>
       <c r="AS91" s="1">
-        <v>9.7200000000000006</v>
+        <v>10.68</v>
       </c>
       <c r="AT91" s="1">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="AU91" s="1">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="AV91" s="1">
-        <v>8.76</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AW91" s="1">
-        <v>10.11</v>
+        <v>10.24</v>
       </c>
       <c r="AX91" s="1">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="AY91" s="1">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="AZ91" s="1">
-        <v>10.196</v>
+        <v>14.31</v>
       </c>
       <c r="BA91" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB91" s="1">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="BC91" s="1">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD91" s="1">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="BE91" s="1">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="BF91" s="1">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="BG91" s="1">
-        <v>4.0999999999999996</v>
+        <v>3.7</v>
       </c>
       <c r="BH91" s="1">
-        <v>12.5</v>
+        <v>54</v>
       </c>
       <c r="BI91" s="1">
-        <v>3.41</v>
+        <v>0.5</v>
       </c>
       <c r="BJ91" s="1" t="s">
         <v>203</v>
       </c>
       <c r="BK91" s="1"/>
       <c r="BL91" s="1" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="BM91" s="1" t="s">
         <v>213</v>
@@ -20311,95 +20920,103 @@
         <v>268</v>
       </c>
       <c r="BU91" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="92" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="92" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2" t="s">
-        <v>413</v>
+        <v>378</v>
       </c>
       <c r="C92" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D92" s="1">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>165</v>
       </c>
       <c r="F92" s="1">
-        <v>1937117349</v>
-      </c>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
+        <v>1972548151</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
+      <c r="K92" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M92" s="1"/>
       <c r="N92" s="1" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="O92" s="1" t="s">
         <v>186</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q92" s="1">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="R92" s="1">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="T92" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U92" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="V92" s="1">
-        <v>102.5</v>
+        <v>104</v>
       </c>
       <c r="W92" s="1">
         <v>15</v>
       </c>
       <c r="X92" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y92" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z92" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA92" s="1" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="AB92" s="1">
-        <v>443</v>
+        <v>196</v>
       </c>
       <c r="AC92" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD92" s="1">
+        <v>110000</v>
+      </c>
+      <c r="AE92" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF92" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="AG92" s="1">
         <v>0</v>
       </c>
-      <c r="AD92" s="1">
-        <v>211000</v>
-      </c>
-      <c r="AE92" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF92" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="AG92" s="1">
-        <v>3</v>
-      </c>
       <c r="AH92" s="1">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="AI92" s="1">
         <v>0</v>
@@ -20411,76 +21028,76 @@
         <v>0</v>
       </c>
       <c r="AL92" s="1">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="AM92" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN92" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO92" s="1">
-        <v>9.56</v>
+        <v>7.91</v>
       </c>
       <c r="AP92" s="1">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="AQ92" s="1">
-        <v>211</v>
+        <v>110</v>
       </c>
       <c r="AR92" s="1">
-        <v>10.78</v>
+        <v>11.98</v>
       </c>
       <c r="AS92" s="1">
-        <v>10.68</v>
+        <v>7.21</v>
       </c>
       <c r="AT92" s="1">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="AU92" s="1">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="AV92" s="1">
-        <v>8.7200000000000006</v>
+        <v>9.41</v>
       </c>
       <c r="AW92" s="1">
-        <v>10.24</v>
+        <v>6.75</v>
       </c>
       <c r="AX92" s="1">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AY92" s="1">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="AZ92" s="1">
-        <v>14.31</v>
+        <v>11.84</v>
       </c>
       <c r="BA92" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB92" s="1">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="BC92" s="1">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="BD92" s="1">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="BE92" s="1">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="BF92" s="1">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="BG92" s="1">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH92" s="1">
-        <v>54</v>
+        <v>6.3</v>
       </c>
       <c r="BI92" s="1">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="BJ92" s="1" t="s">
         <v>203</v>
@@ -20490,67 +21107,79 @@
         <v>203</v>
       </c>
       <c r="BM92" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="BN92" s="1"/>
       <c r="BO92" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BP92" s="1" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
       <c r="BQ92" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR92" s="1" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="BS92" s="1"/>
       <c r="BT92" s="1" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="BU92" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="93" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="93" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C93" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D93" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>165</v>
+        <v>342</v>
       </c>
       <c r="F93" s="1">
-        <v>1972548151</v>
-      </c>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="1"/>
+        <v>1320725584</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1" t="s">
         <v>247</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q93" s="1">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="R93" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="S93" s="1" t="s">
         <v>184</v>
@@ -20559,49 +21188,49 @@
         <v>90</v>
       </c>
       <c r="U93" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="V93" s="1">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="W93" s="1">
         <v>15</v>
       </c>
       <c r="X93" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y93" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Z93" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AA93" s="1" t="s">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="AB93" s="1">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="AC93" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD93" s="1">
-        <v>110000</v>
+        <v>210000</v>
       </c>
       <c r="AE93" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="AG93" s="1">
         <v>1</v>
       </c>
-      <c r="AF93" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="AG93" s="1">
-        <v>0</v>
-      </c>
       <c r="AH93" s="1">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AI93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ93" s="1">
         <v>15</v>
@@ -20610,76 +21239,76 @@
         <v>0</v>
       </c>
       <c r="AL93" s="1">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="AM93" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN93" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO93" s="1">
-        <v>7.91</v>
+        <v>10.98</v>
       </c>
       <c r="AP93" s="1">
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AQ93" s="1">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="AR93" s="1">
-        <v>11.98</v>
+        <v>9.0150000000000006</v>
       </c>
       <c r="AS93" s="1">
-        <v>7.21</v>
+        <v>10.6</v>
       </c>
       <c r="AT93" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="AU93" s="1">
+        <v>170</v>
+      </c>
+      <c r="AV93" s="1">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="AW93" s="1">
+        <v>11.1</v>
+      </c>
+      <c r="AX93" s="1">
         <v>0.73</v>
       </c>
-      <c r="AU93" s="1">
-        <v>105</v>
-      </c>
-      <c r="AV93" s="1">
-        <v>9.41</v>
-      </c>
-      <c r="AW93" s="1">
-        <v>6.75</v>
-      </c>
-      <c r="AX93" s="1">
-        <v>0.6</v>
-      </c>
       <c r="AY93" s="1">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AZ93" s="1">
-        <v>11.84</v>
+        <v>10.86</v>
       </c>
       <c r="BA93" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB93" s="1">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="BC93" s="1">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="BD93" s="1">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE93" s="1">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="BF93" s="1">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="BG93" s="1">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="BH93" s="1">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="BI93" s="1">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="BJ93" s="1" t="s">
         <v>203</v>
@@ -20689,51 +21318,51 @@
         <v>203</v>
       </c>
       <c r="BM93" s="1" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="BN93" s="1"/>
       <c r="BO93" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BP93" s="1" t="s">
-        <v>329</v>
+        <v>486</v>
       </c>
       <c r="BQ93" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR93" s="1" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="BS93" s="1"/>
       <c r="BT93" s="1" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="BU93" s="2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="94" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="94" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C94" s="1">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D94" s="1">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>343</v>
+        <v>254</v>
       </c>
       <c r="F94" s="1">
-        <v>1320725584</v>
+        <v>1723249312</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>257</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>211</v>
@@ -20742,7 +21371,7 @@
         <v>211</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="L94" s="1" t="s">
         <v>211</v>
@@ -20758,7 +21387,7 @@
         <v>258</v>
       </c>
       <c r="Q94" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R94" s="1">
         <v>92</v>
@@ -20767,13 +21396,13 @@
         <v>184</v>
       </c>
       <c r="T94" s="1">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="U94" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="V94" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="W94" s="1">
         <v>15</v>
@@ -20782,37 +21411,37 @@
         <v>9</v>
       </c>
       <c r="Y94" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z94" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA94" s="1" t="s">
         <v>212</v>
       </c>
       <c r="AB94" s="1">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="AC94" s="1">
         <v>2</v>
       </c>
       <c r="AD94" s="1">
-        <v>210000</v>
+        <v>320000</v>
       </c>
       <c r="AE94" s="1">
         <v>0</v>
       </c>
       <c r="AF94" s="1">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AG94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH94" s="1">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="AI94" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ94" s="1">
         <v>15</v>
@@ -20821,73 +21450,73 @@
         <v>0</v>
       </c>
       <c r="AL94" s="1">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AM94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN94" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO94" s="1">
-        <v>10.98</v>
+        <v>4.2</v>
       </c>
       <c r="AP94" s="1">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="AQ94" s="1">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="AR94" s="1">
-        <v>9.0150000000000006</v>
+        <v>6.36</v>
       </c>
       <c r="AS94" s="1">
-        <v>10.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT94" s="1">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="AU94" s="1">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AV94" s="1">
-        <v>8.7799999999999994</v>
+        <v>9.43</v>
       </c>
       <c r="AW94" s="1">
-        <v>11.1</v>
+        <v>8.64</v>
       </c>
       <c r="AX94" s="1">
-        <v>0.73</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AY94" s="1">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="AZ94" s="1">
-        <v>10.86</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="BA94" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB94" s="1">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="BC94" s="1">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="BD94" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="BE94" s="1">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BF94" s="1">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="BG94" s="1">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BH94" s="1">
-        <v>14.3</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="BI94" s="1">
         <v>0.5</v>
@@ -20900,51 +21529,51 @@
         <v>203</v>
       </c>
       <c r="BM94" s="1" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="BN94" s="1"/>
       <c r="BO94" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BP94" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="BQ94" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR94" s="1" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="BS94" s="1"/>
       <c r="BT94" s="1" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="BU94" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="95" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="95" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C95" s="1">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D95" s="1">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>254</v>
       </c>
       <c r="F95" s="1">
-        <v>1723249312</v>
+        <v>17234035673</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>211</v>
@@ -20953,47 +21582,49 @@
         <v>211</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M95" s="1"/>
+      <c r="M95" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="N95" s="1" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>241</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="Q95" s="1">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R95" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="S95" s="1" t="s">
         <v>184</v>
       </c>
       <c r="T95" s="1">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="U95" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="V95" s="1">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="W95" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X95" s="1">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y95" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z95" s="1">
         <v>17</v>
@@ -21002,106 +21633,106 @@
         <v>212</v>
       </c>
       <c r="AB95" s="1">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="AC95" s="1">
         <v>2</v>
       </c>
       <c r="AD95" s="1">
-        <v>320000</v>
+        <v>186000</v>
       </c>
       <c r="AE95" s="1">
         <v>0</v>
       </c>
       <c r="AF95" s="1">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AG95" s="1">
         <v>0</v>
       </c>
-      <c r="AH95" s="1">
-        <v>90</v>
+      <c r="AH95" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="AI95" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ95" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL95" s="1">
-        <v>2.1</v>
+        <v>3.72</v>
       </c>
       <c r="AM95" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN95" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AO95" s="1">
-        <v>4.2</v>
+        <v>25.6</v>
       </c>
       <c r="AP95" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="AQ95" s="1">
+        <v>186</v>
+      </c>
+      <c r="AR95" s="1">
+        <v>14.34</v>
+      </c>
+      <c r="AS95" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="AT95" s="1">
+        <v>1</v>
+      </c>
+      <c r="AU95" s="1">
+        <v>150</v>
+      </c>
+      <c r="AV95" s="1">
+        <v>14.33</v>
+      </c>
+      <c r="AW95" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AX95" s="1">
         <v>0.6</v>
       </c>
-      <c r="AQ95" s="1">
-        <v>110</v>
-      </c>
-      <c r="AR95" s="1">
-        <v>6.36</v>
-      </c>
-      <c r="AS95" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="AT95" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="AU95" s="1">
-        <v>100</v>
-      </c>
-      <c r="AV95" s="1">
-        <v>9.43</v>
-      </c>
-      <c r="AW95" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="AX95" s="1">
-        <v>0.56000000000000005</v>
-      </c>
       <c r="AY95" s="1">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="AZ95" s="1">
-        <v>17.239999999999998</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="BA95" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB95" s="1">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="BC95" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BD95" s="1">
-        <v>43</v>
+        <v>0.6</v>
       </c>
       <c r="BE95" s="1">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="BF95" s="1">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="BG95" s="1">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH95" s="1">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BI95" s="1">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="BJ95" s="1" t="s">
         <v>203</v>
@@ -21111,123 +21742,119 @@
         <v>203</v>
       </c>
       <c r="BM95" s="1" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="BN95" s="1"/>
       <c r="BO95" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BP95" s="1" t="s">
-        <v>493</v>
+        <v>214</v>
       </c>
       <c r="BQ95" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR95" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="BS95" s="1"/>
+        <v>250</v>
+      </c>
+      <c r="BS95" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="BT95" s="1" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="BU95" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="96" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="96" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2" t="s">
-        <v>413</v>
+        <v>340</v>
       </c>
       <c r="C96" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D96" s="1">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="F96" s="1">
-        <v>17234035673</v>
+        <v>1752083265</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>211</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
       <c r="K96" s="1" t="s">
         <v>211</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>211</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="M96" s="1"/>
       <c r="N96" s="1" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>241</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>231</v>
+        <v>187</v>
       </c>
       <c r="Q96" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R96" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="T96" s="1">
         <v>80</v>
       </c>
       <c r="U96" s="1">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="V96" s="1">
-        <v>100.5</v>
+        <v>101.5</v>
       </c>
       <c r="W96" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X96" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y96" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z96" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA96" s="1" t="s">
         <v>212</v>
       </c>
       <c r="AB96" s="1">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="AC96" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD96" s="1">
-        <v>186000</v>
+        <v>112000</v>
       </c>
       <c r="AE96" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF96" s="1">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AG96" s="1">
         <v>0</v>
@@ -21239,82 +21866,82 @@
         <v>3</v>
       </c>
       <c r="AJ96" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK96" s="1">
         <v>1</v>
       </c>
       <c r="AL96" s="1">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AM96" s="1">
         <v>3</v>
       </c>
       <c r="AN96" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO96" s="1">
-        <v>25.6</v>
+        <v>11.2</v>
       </c>
       <c r="AP96" s="1">
-        <v>0.96</v>
+        <v>0.42</v>
       </c>
       <c r="AQ96" s="1">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="AR96" s="1">
-        <v>14.34</v>
+        <v>23.81</v>
       </c>
       <c r="AS96" s="1">
-        <v>21.5</v>
+        <v>6.24</v>
       </c>
       <c r="AT96" s="1">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU96" s="1">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="AV96" s="1">
-        <v>14.33</v>
+        <v>6.5</v>
       </c>
       <c r="AW96" s="1">
-        <v>17.399999999999999</v>
+        <v>12</v>
       </c>
       <c r="AX96" s="1">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="AY96" s="1">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="AZ96" s="1">
-        <v>20.420000000000002</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="BA96" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB96" s="1">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="BC96" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="BD96" s="1">
-        <v>0.6</v>
+        <v>42</v>
       </c>
       <c r="BE96" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BF96" s="1">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="BG96" s="1">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH96" s="1">
-        <v>7.2</v>
+        <v>12.9</v>
       </c>
       <c r="BI96" s="1">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="BJ96" s="1" t="s">
         <v>203</v>
@@ -21324,7 +21951,7 @@
         <v>203</v>
       </c>
       <c r="BM96" s="1" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="BN96" s="1"/>
       <c r="BO96" s="1" t="s">
@@ -21343,179 +21970,187 @@
         <v>216</v>
       </c>
       <c r="BT96" s="1" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="BU96" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="97" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="97" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="2" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="C97" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D97" s="1">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F97" s="1">
-        <v>1752083265</v>
-      </c>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
+        <v>1789078051</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
+      <c r="K97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="O97" s="1" t="s">
         <v>241</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="Q97" s="1">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="R97" s="1">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S97" s="1" t="s">
-        <v>252</v>
+        <v>184</v>
       </c>
       <c r="T97" s="1">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="U97" s="1">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="V97" s="1">
-        <v>101.5</v>
+        <v>102</v>
       </c>
       <c r="W97" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X97" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y97" s="1">
         <v>10</v>
       </c>
       <c r="Z97" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA97" s="1" t="s">
         <v>212</v>
       </c>
       <c r="AB97" s="1">
-        <v>326</v>
+        <v>259</v>
       </c>
       <c r="AC97" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD97" s="1">
-        <v>112000</v>
+        <v>420000</v>
       </c>
       <c r="AE97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF97" s="1">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AG97" s="1">
         <v>0</v>
       </c>
-      <c r="AH97" s="1" t="s">
-        <v>251</v>
+      <c r="AH97" s="1">
+        <v>73</v>
       </c>
       <c r="AI97" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ97" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL97" s="1">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="AM97" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN97" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AO97" s="1">
-        <v>11.2</v>
+        <v>26.88</v>
       </c>
       <c r="AP97" s="1">
-        <v>0.42</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AQ97" s="1">
-        <v>112</v>
+        <v>420</v>
       </c>
       <c r="AR97" s="1">
-        <v>23.81</v>
+        <v>11.4</v>
       </c>
       <c r="AS97" s="1">
-        <v>6.24</v>
+        <v>21.36</v>
       </c>
       <c r="AT97" s="1">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="AU97" s="1">
-        <v>109</v>
+        <v>310</v>
       </c>
       <c r="AV97" s="1">
-        <v>6.5</v>
+        <v>9.57</v>
       </c>
       <c r="AW97" s="1">
-        <v>12</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="AX97" s="1">
-        <v>2.4</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AY97" s="1">
-        <v>58</v>
+        <v>190</v>
       </c>
       <c r="AZ97" s="1">
-        <v>8.6199999999999992</v>
+        <v>16.32</v>
       </c>
       <c r="BA97" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB97" s="1">
-        <v>2.17</v>
+        <v>1.38</v>
       </c>
       <c r="BC97" s="1">
         <v>0.7</v>
       </c>
       <c r="BD97" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BE97" s="1">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="BF97" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BG97" s="1">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BH97" s="1">
-        <v>12.9</v>
+        <v>7.8</v>
       </c>
       <c r="BI97" s="1">
-        <v>4.0999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="BJ97" s="1" t="s">
         <v>203</v>
@@ -21532,190 +22167,192 @@
         <v>206</v>
       </c>
       <c r="BP97" s="1" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="BQ97" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR97" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="BS97" s="1" t="s">
-        <v>216</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="BS97" s="1"/>
       <c r="BT97" s="1" t="s">
         <v>229</v>
       </c>
       <c r="BU97" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="98" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="98" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="2" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C98" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" s="1">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F98" s="1">
-        <v>1789078051</v>
-      </c>
-      <c r="G98" s="1"/>
+        <v>1791877134</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="H98" s="1" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
+      <c r="K98" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="P98" s="1" t="s">
-        <v>224</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="P98" s="1"/>
       <c r="Q98" s="1">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="R98" s="1">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="T98" s="1">
         <v>120</v>
       </c>
       <c r="U98" s="1">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="V98" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W98" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X98" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y98" s="1">
         <v>10</v>
       </c>
       <c r="Z98" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA98" s="1" t="s">
         <v>212</v>
       </c>
       <c r="AB98" s="1">
-        <v>259</v>
+        <v>369</v>
       </c>
       <c r="AC98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD98" s="1">
-        <v>420000</v>
+        <v>180000</v>
       </c>
       <c r="AE98" s="1">
         <v>0</v>
       </c>
       <c r="AF98" s="1">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="AG98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH98" s="1">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AI98" s="1">
         <v>0</v>
       </c>
       <c r="AJ98" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AK98" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL98" s="1">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AM98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN98" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO98" s="1">
-        <v>26.88</v>
+        <v>14.6</v>
       </c>
       <c r="AP98" s="1">
-        <v>0.56000000000000005</v>
+        <v>0.68</v>
       </c>
       <c r="AQ98" s="1">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="AR98" s="1">
-        <v>11.4</v>
+        <v>11.94</v>
       </c>
       <c r="AS98" s="1">
-        <v>21.36</v>
+        <v>13.6</v>
       </c>
       <c r="AT98" s="1">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="AU98" s="1">
-        <v>310</v>
+        <v>172</v>
       </c>
       <c r="AV98" s="1">
-        <v>9.57</v>
+        <v>9.8800000000000008</v>
       </c>
       <c r="AW98" s="1">
-        <v>17.670000000000002</v>
+        <v>13.6</v>
       </c>
       <c r="AX98" s="1">
-        <v>0.56999999999999995</v>
+        <v>0.8</v>
       </c>
       <c r="AY98" s="1">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AZ98" s="1">
-        <v>16.32</v>
+        <v>12.14</v>
       </c>
       <c r="BA98" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB98" s="1">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="BC98" s="1">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="BD98" s="1">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="BE98" s="1">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="BF98" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BG98" s="1">
-        <v>4.9000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="BH98" s="1">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="BI98" s="1">
         <v>0.5</v>
@@ -21728,116 +22365,132 @@
         <v>203</v>
       </c>
       <c r="BM98" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="BN98" s="1"/>
+        <v>213</v>
+      </c>
+      <c r="BN98" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="BO98" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BP98" s="1" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="BQ98" s="1" t="s">
         <v>206</v>
       </c>
       <c r="BR98" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="BS98" s="1"/>
+        <v>215</v>
+      </c>
+      <c r="BS98" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="BT98" s="1" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="BU98" s="2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="99" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="99" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="B99" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C99" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99" s="1">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F99" s="1">
-        <v>1791877134</v>
-      </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
+        <v>1737477741</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
+      <c r="K99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1" t="s">
         <v>176</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="P99" s="1"/>
+        <v>241</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="Q99" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R99" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S99" s="1" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="T99" s="1">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="U99" s="1">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="V99" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W99" s="1">
         <v>12</v>
       </c>
       <c r="X99" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y99" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z99" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA99" s="1" t="s">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="AB99" s="1">
-        <v>369</v>
+        <v>259</v>
       </c>
       <c r="AC99" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD99" s="1">
+        <v>115000</v>
+      </c>
+      <c r="AE99" s="1">
         <v>1</v>
       </c>
-      <c r="AD99" s="1">
-        <v>180000</v>
-      </c>
-      <c r="AE99" s="1">
+      <c r="AF99" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="AG99" s="1">
         <v>0</v>
       </c>
-      <c r="AF99" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="AG99" s="1">
+      <c r="AH99" s="1">
+        <v>63</v>
+      </c>
+      <c r="AI99" s="1">
         <v>1</v>
-      </c>
-      <c r="AH99" s="1">
-        <v>93</v>
-      </c>
-      <c r="AI99" s="1">
-        <v>0</v>
       </c>
       <c r="AJ99" s="1">
         <v>12</v>
@@ -21846,76 +22499,76 @@
         <v>2</v>
       </c>
       <c r="AL99" s="1">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AM99" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN99" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO99" s="1">
-        <v>14.6</v>
+        <v>11.2</v>
       </c>
       <c r="AP99" s="1">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="AQ99" s="1">
-        <v>180</v>
+        <v>115</v>
       </c>
       <c r="AR99" s="1">
-        <v>11.94</v>
+        <v>9.94</v>
       </c>
       <c r="AS99" s="1">
-        <v>13.6</v>
+        <v>12.69</v>
       </c>
       <c r="AT99" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AU99" s="1">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="AV99" s="1">
-        <v>9.8800000000000008</v>
+        <v>13.33</v>
       </c>
       <c r="AW99" s="1">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="AX99" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AY99" s="1">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AZ99" s="1">
-        <v>12.14</v>
+        <v>17.89</v>
       </c>
       <c r="BA99" s="1" t="s">
         <v>201</v>
       </c>
       <c r="BB99" s="1">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="BC99" s="1">
         <v>0.8</v>
       </c>
       <c r="BD99" s="1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="BE99" s="1">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF99" s="1">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="BG99" s="1">
         <v>4.2</v>
       </c>
       <c r="BH99" s="1">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI99" s="1">
-        <v>0.5</v>
+        <v>1.39</v>
       </c>
       <c r="BJ99" s="1" t="s">
         <v>203</v>
@@ -21943,245 +22596,253 @@
         <v>215</v>
       </c>
       <c r="BS99" s="1" t="s">
-        <v>216</v>
+        <v>273</v>
       </c>
       <c r="BT99" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="BU99" s="2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="100" spans="1:73" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>398</v>
-      </c>
+        <v>482</v>
+      </c>
+    </row>
+    <row r="100" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
       <c r="B100" s="2" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C100" s="1">
         <v>3</v>
       </c>
       <c r="D100" s="1">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F100" s="1">
-        <v>1737477741</v>
-      </c>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
+        <v>1715568573</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
+      <c r="K100" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1" t="s">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="Q100" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R100" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="T100" s="1">
         <v>90</v>
       </c>
       <c r="U100" s="1">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="V100" s="1">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="W100" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X100" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y100" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z100" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AA100" s="1" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="AB100" s="1">
-        <v>259</v>
+        <v>400</v>
       </c>
       <c r="AC100" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="1">
-        <v>115000</v>
+        <v>158000</v>
       </c>
       <c r="AE100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="1">
         <v>1</v>
-      </c>
-      <c r="AF100" s="1">
-        <v>0.8</v>
       </c>
       <c r="AG100" s="1">
         <v>0</v>
       </c>
       <c r="AH100" s="1">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="AI100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="1">
+        <v>14</v>
+      </c>
+      <c r="AK100" s="1">
         <v>1</v>
       </c>
-      <c r="AJ100" s="1">
-        <v>12</v>
-      </c>
-      <c r="AK100" s="1">
+      <c r="AL100" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="AM100" s="1">
+        <v>1</v>
+      </c>
+      <c r="AN100" s="1">
         <v>2</v>
       </c>
-      <c r="AL100" s="1">
-        <v>2.4</v>
-      </c>
-      <c r="AM100" s="1">
-        <v>2</v>
-      </c>
-      <c r="AN100" s="1">
-        <v>6</v>
-      </c>
       <c r="AO100" s="1">
-        <v>11.2</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="AP100" s="1">
-        <v>0.98</v>
+        <v>0.6</v>
       </c>
       <c r="AQ100" s="1">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="AR100" s="1">
-        <v>9.94</v>
+        <v>10.5</v>
       </c>
       <c r="AS100" s="1">
-        <v>12.69</v>
+        <v>8.56</v>
       </c>
       <c r="AT100" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AU100" s="1">
-        <v>105</v>
+        <v>6.03</v>
       </c>
       <c r="AV100" s="1">
-        <v>13.33</v>
+        <v>7.85</v>
       </c>
       <c r="AW100" s="1">
-        <v>15.3</v>
+        <v>7.85</v>
       </c>
       <c r="AX100" s="1">
         <v>0.9</v>
       </c>
       <c r="AY100" s="1">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AZ100" s="1">
-        <v>17.89</v>
+        <v>3.79</v>
       </c>
       <c r="BA100" s="1" t="s">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="BB100" s="1">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="BC100" s="1">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BD100" s="1">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="BE100" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BF100" s="1">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="BG100" s="1">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH100" s="1">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BI100" s="1">
-        <v>1.39</v>
+        <v>0.5</v>
       </c>
       <c r="BJ100" s="1" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="BK100" s="1"/>
       <c r="BL100" s="1" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="BM100" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="BN100" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="BN100" s="1"/>
       <c r="BO100" s="1" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="BP100" s="1" t="s">
         <v>214</v>
       </c>
       <c r="BQ100" s="1" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="BR100" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="BS100" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="BS100" s="1"/>
       <c r="BT100" s="1" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="BU100" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="101" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C101" s="1">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D101" s="1">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F101" s="1">
-        <v>1715568573</v>
+        <v>1740248357</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H101" s="1"/>
+      <c r="H101" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
+      <c r="K101" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1" t="s">
         <v>233</v>
@@ -22193,7 +22854,7 @@
         <v>240</v>
       </c>
       <c r="Q101" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R101" s="1">
         <v>96</v>
@@ -22202,22 +22863,22 @@
         <v>211</v>
       </c>
       <c r="T101" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U101" s="1">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="V101" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="W101" s="1">
         <v>15</v>
       </c>
       <c r="X101" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y101" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z101" s="1">
         <v>1</v>
@@ -22232,13 +22893,13 @@
         <v>0</v>
       </c>
       <c r="AD101" s="1">
-        <v>158000</v>
+        <v>152000</v>
       </c>
       <c r="AE101" s="1">
         <v>0</v>
       </c>
       <c r="AF101" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AG101" s="1">
         <v>0</v>
@@ -22250,79 +22911,79 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK101" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL101" s="1">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AM101" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN101" s="1">
         <v>2</v>
       </c>
       <c r="AO101" s="1">
-        <v>9.9600000000000009</v>
+        <v>13.56</v>
       </c>
       <c r="AP101" s="1">
         <v>0.6</v>
       </c>
       <c r="AQ101" s="1">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="AR101" s="1">
-        <v>10.5</v>
+        <v>14.86</v>
       </c>
       <c r="AS101" s="1">
-        <v>8.56</v>
+        <v>10.83</v>
       </c>
       <c r="AT101" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AU101" s="1">
-        <v>6.03</v>
+        <v>195</v>
       </c>
       <c r="AV101" s="1">
-        <v>7.85</v>
+        <v>6.17</v>
       </c>
       <c r="AW101" s="1">
-        <v>7.85</v>
+        <v>11.21</v>
       </c>
       <c r="AX101" s="1">
-        <v>0.9</v>
+        <v>1.25</v>
       </c>
       <c r="AY101" s="1">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="AZ101" s="1">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="BA101" s="1" t="s">
         <v>239</v>
       </c>
       <c r="BB101" s="1">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="BC101" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BD101" s="1">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE101" s="1">
         <v>33</v>
       </c>
       <c r="BF101" s="1">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="BG101" s="1">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="BH101" s="1">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="BI101" s="1">
         <v>0.5</v>
@@ -22348,41 +23009,47 @@
         <v>235</v>
       </c>
       <c r="BR101" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS101" s="1"/>
       <c r="BT101" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU101" s="2" t="s">
-        <v>486</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="2" t="s">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="C102" s="1">
         <v>29</v>
       </c>
       <c r="D102" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F102" s="1">
-        <v>1740248357</v>
+        <v>1919932482</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H102" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="1"/>
+      <c r="K102" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M102" s="1"/>
       <c r="N102" s="1" t="s">
         <v>233</v>
@@ -22394,52 +23061,52 @@
         <v>240</v>
       </c>
       <c r="Q102" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R102" s="1">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S102" s="1" t="s">
         <v>211</v>
       </c>
       <c r="T102" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U102" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="V102" s="1">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="W102" s="1">
         <v>15</v>
       </c>
       <c r="X102" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y102" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z102" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA102" s="1" t="s">
         <v>239</v>
       </c>
       <c r="AB102" s="1">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="AC102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD102" s="1">
-        <v>152000</v>
+        <v>146000</v>
       </c>
       <c r="AE102" s="1">
         <v>0</v>
       </c>
       <c r="AF102" s="1">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AG102" s="1">
         <v>0</v>
@@ -22451,55 +23118,55 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL102" s="1">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AM102" s="1">
         <v>2</v>
       </c>
       <c r="AN102" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO102" s="1">
-        <v>13.56</v>
+        <v>13.64</v>
       </c>
       <c r="AP102" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AQ102" s="1">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="AR102" s="1">
-        <v>14.86</v>
+        <v>13.34</v>
       </c>
       <c r="AS102" s="1">
-        <v>10.83</v>
+        <v>11.92</v>
       </c>
       <c r="AT102" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AU102" s="1">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AV102" s="1">
-        <v>6.17</v>
+        <v>7.84</v>
       </c>
       <c r="AW102" s="1">
-        <v>11.21</v>
+        <v>11.49</v>
       </c>
       <c r="AX102" s="1">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AY102" s="1">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AZ102" s="1">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="BA102" s="1" t="s">
         <v>239</v>
@@ -22511,19 +23178,19 @@
         <v>0.9</v>
       </c>
       <c r="BD102" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BE102" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BF102" s="1">
         <v>147</v>
       </c>
       <c r="BG102" s="1">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="BH102" s="1">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="BI102" s="1">
         <v>0.5</v>
@@ -22549,39 +23216,47 @@
         <v>235</v>
       </c>
       <c r="BR102" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS102" s="1"/>
       <c r="BT102" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU102" s="2" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
     </row>
     <row r="103" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C103" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D103" s="1">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>343</v>
+        <v>165</v>
       </c>
       <c r="F103" s="1">
-        <v>1919932482</v>
-      </c>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
+        <v>1774185410</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
+      <c r="K103" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="M103" s="1"/>
       <c r="N103" s="1" t="s">
         <v>233</v>
@@ -22593,7 +23268,7 @@
         <v>240</v>
       </c>
       <c r="Q103" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R103" s="1">
         <v>94</v>
@@ -22605,7 +23280,7 @@
         <v>90</v>
       </c>
       <c r="U103" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V103" s="1">
         <v>99</v>
@@ -22632,7 +23307,7 @@
         <v>1</v>
       </c>
       <c r="AD103" s="1">
-        <v>146000</v>
+        <v>152000</v>
       </c>
       <c r="AE103" s="1">
         <v>0</v>
@@ -22650,70 +23325,70 @@
         <v>0</v>
       </c>
       <c r="AJ103" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL103" s="1">
-        <v>2.2000000000000002</v>
+        <v>2.69</v>
       </c>
       <c r="AM103" s="1">
         <v>2</v>
       </c>
       <c r="AN103" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO103" s="1">
-        <v>13.64</v>
+        <v>8.67</v>
       </c>
       <c r="AP103" s="1">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="AQ103" s="1">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AR103" s="1">
-        <v>13.34</v>
+        <v>11.88</v>
       </c>
       <c r="AS103" s="1">
-        <v>11.92</v>
+        <v>7.83</v>
       </c>
       <c r="AT103" s="1">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="AU103" s="1">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AV103" s="1">
-        <v>7.84</v>
+        <v>6.11</v>
       </c>
       <c r="AW103" s="1">
-        <v>11.49</v>
+        <v>6.58</v>
       </c>
       <c r="AX103" s="1">
-        <v>1.21</v>
+        <v>0.9</v>
       </c>
       <c r="AY103" s="1">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AZ103" s="1">
-        <v>3.39</v>
+        <v>2.7</v>
       </c>
       <c r="BA103" s="1" t="s">
         <v>239</v>
       </c>
       <c r="BB103" s="1">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="BC103" s="1">
         <v>0.9</v>
       </c>
       <c r="BD103" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BE103" s="1">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF103" s="1">
         <v>147</v>
@@ -22722,7 +23397,7 @@
         <v>4.3</v>
       </c>
       <c r="BH103" s="1">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="BI103" s="1">
         <v>0.5</v>
@@ -22748,60 +23423,60 @@
         <v>235</v>
       </c>
       <c r="BR103" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS103" s="1"/>
       <c r="BT103" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU103" s="2" t="s">
-        <v>430</v>
+        <v>349</v>
       </c>
     </row>
     <row r="104" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="2" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
       <c r="C104" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D104" s="1">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>165</v>
+        <v>342</v>
       </c>
       <c r="F104" s="1">
-        <v>1774185410</v>
+        <v>1780995591</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="L104" s="1"/>
+      <c r="L104" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="M104" s="1"/>
       <c r="N104" s="1" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P104" s="1" t="s">
-        <v>240</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="P104" s="1"/>
       <c r="Q104" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R104" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S104" s="1" t="s">
         <v>211</v>
@@ -22810,10 +23485,10 @@
         <v>90</v>
       </c>
       <c r="U104" s="1">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="V104" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W104" s="1">
         <v>15</v>
@@ -22822,7 +23497,7 @@
         <v>7</v>
       </c>
       <c r="Y104" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z104" s="1">
         <v>2</v>
@@ -22831,103 +23506,103 @@
         <v>239</v>
       </c>
       <c r="AB104" s="1">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="AC104" s="1">
         <v>1</v>
       </c>
       <c r="AD104" s="1">
-        <v>152000</v>
+        <v>149000</v>
       </c>
       <c r="AE104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF104" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AG104" s="1">
         <v>0</v>
       </c>
       <c r="AH104" s="1">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AI104" s="1">
         <v>0</v>
       </c>
       <c r="AJ104" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL104" s="1">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AM104" s="1">
         <v>2</v>
       </c>
       <c r="AN104" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO104" s="1">
-        <v>8.67</v>
+        <v>9.27</v>
       </c>
       <c r="AP104" s="1">
-        <v>0.48</v>
+        <v>0.62</v>
       </c>
       <c r="AQ104" s="1">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AR104" s="1">
-        <v>11.88</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="AS104" s="1">
-        <v>7.83</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="AT104" s="1">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AU104" s="1">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="AV104" s="1">
-        <v>6.11</v>
+        <v>6.79</v>
       </c>
       <c r="AW104" s="1">
-        <v>6.58</v>
+        <v>7.2</v>
       </c>
       <c r="AX104" s="1">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AY104" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AZ104" s="1">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="BA104" s="1" t="s">
         <v>239</v>
       </c>
       <c r="BB104" s="1">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="BC104" s="1">
         <v>0.9</v>
       </c>
       <c r="BD104" s="1">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="BE104" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BF104" s="1">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="BG104" s="1">
         <v>4.3</v>
       </c>
       <c r="BH104" s="1">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="BI104" s="1">
         <v>0.5</v>
@@ -22953,52 +23628,62 @@
         <v>235</v>
       </c>
       <c r="BR104" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BS104" s="1"/>
       <c r="BT104" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU104" s="2" t="s">
-        <v>350</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="2" t="s">
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="C105" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" s="1">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F105" s="1">
-        <v>1780995591</v>
-      </c>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
+        <v>1724676912</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
+      <c r="K105" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="M105" s="1"/>
       <c r="N105" s="1" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="P105" s="1"/>
+        <v>184</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>297</v>
+      </c>
       <c r="Q105" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R105" s="1">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S105" s="1" t="s">
         <v>211</v>
@@ -23007,19 +23692,19 @@
         <v>90</v>
       </c>
       <c r="U105" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="V105" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="W105" s="1">
         <v>15</v>
       </c>
       <c r="X105" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y105" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z105" s="1">
         <v>2</v>
@@ -23028,340 +23713,212 @@
         <v>239</v>
       </c>
       <c r="AB105" s="1">
-        <v>369</v>
+        <v>326</v>
       </c>
       <c r="AC105" s="1">
         <v>1</v>
       </c>
       <c r="AD105" s="1">
-        <v>149000</v>
+        <v>130000</v>
       </c>
       <c r="AE105" s="1">
         <v>1</v>
       </c>
       <c r="AF105" s="1">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="AG105" s="1">
         <v>0</v>
       </c>
       <c r="AH105" s="1">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="AI105" s="1">
         <v>0</v>
       </c>
       <c r="AJ105" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL105" s="1">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="AM105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN105" s="1">
         <v>2</v>
       </c>
-      <c r="AN105" s="1">
-        <v>5</v>
-      </c>
       <c r="AO105" s="1">
-        <v>9.27</v>
+        <v>21.37</v>
       </c>
       <c r="AP105" s="1">
-        <v>0.62</v>
+        <v>1.56</v>
       </c>
       <c r="AQ105" s="1">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="AR105" s="1">
-        <v>10.029999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="AS105" s="1">
-        <v>8.4499999999999993</v>
+        <v>19.350000000000001</v>
       </c>
       <c r="AT105" s="1">
-        <v>0.74</v>
+        <v>1.81</v>
       </c>
       <c r="AU105" s="1">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AV105" s="1">
-        <v>6.79</v>
+        <v>6.32</v>
       </c>
       <c r="AW105" s="1">
-        <v>7.2</v>
+        <v>11.95</v>
       </c>
       <c r="AX105" s="1">
-        <v>0.92</v>
+        <v>1.3</v>
       </c>
       <c r="AY105" s="1">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AZ105" s="1">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="BA105" s="1" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="BB105" s="1">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="BC105" s="1">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="BD105" s="1">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="BE105" s="1">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BF105" s="1">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="BG105" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH105" s="1">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="BI105" s="1">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="BJ105" s="1" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="BK105" s="1"/>
       <c r="BL105" s="1" t="s">
         <v>222</v>
       </c>
       <c r="BM105" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="BN105" s="1"/>
       <c r="BO105" s="1" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="BP105" s="1" t="s">
-        <v>214</v>
+        <v>488</v>
       </c>
       <c r="BQ105" s="1" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="BR105" s="1" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="BS105" s="1"/>
       <c r="BT105" s="1" t="s">
         <v>237</v>
       </c>
       <c r="BU105" s="2" t="s">
-        <v>408</v>
+        <v>492</v>
       </c>
     </row>
     <row r="106" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
-      <c r="B106" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C106" s="1">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1">
-        <v>67</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F106" s="1">
-        <v>1724676912</v>
-      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-      <c r="H106" s="1" t="s">
-        <v>241</v>
-      </c>
+      <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
-      <c r="L106" s="1" t="s">
-        <v>241</v>
-      </c>
+      <c r="L106" s="1"/>
       <c r="M106" s="1"/>
-      <c r="N106" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="P106" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q106" s="1">
-        <v>28</v>
-      </c>
-      <c r="R106" s="1">
-        <v>93</v>
-      </c>
-      <c r="S106" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="T106" s="1">
-        <v>90</v>
-      </c>
-      <c r="U106" s="1">
-        <v>100</v>
-      </c>
-      <c r="V106" s="1">
-        <v>100</v>
-      </c>
-      <c r="W106" s="1">
-        <v>15</v>
-      </c>
-      <c r="X106" s="1">
-        <v>9</v>
-      </c>
-      <c r="Y106" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z106" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA106" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AB106" s="1">
-        <v>326</v>
-      </c>
-      <c r="AC106" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD106" s="1">
-        <v>130000</v>
-      </c>
-      <c r="AE106" s="1">
-        <v>1</v>
-      </c>
-      <c r="AF106" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="AG106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH106" s="1">
-        <v>70</v>
-      </c>
-      <c r="AI106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ106" s="1">
-        <v>15</v>
-      </c>
-      <c r="AK106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL106" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="AM106" s="1">
-        <v>0</v>
-      </c>
-      <c r="AN106" s="1">
-        <v>2</v>
-      </c>
-      <c r="AO106" s="1">
-        <v>21.37</v>
-      </c>
-      <c r="AP106" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="AQ106" s="1">
-        <v>130</v>
-      </c>
-      <c r="AR106" s="1">
-        <v>10.53</v>
-      </c>
-      <c r="AS106" s="1">
-        <v>19.350000000000001</v>
-      </c>
-      <c r="AT106" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="AU106" s="1">
-        <v>169</v>
-      </c>
-      <c r="AV106" s="1">
-        <v>6.32</v>
-      </c>
-      <c r="AW106" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="AX106" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="AY106" s="1">
-        <v>280</v>
-      </c>
-      <c r="AZ106" s="1">
-        <v>3.28</v>
-      </c>
-      <c r="BA106" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="BB106" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="BC106" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="BD106" s="1">
-        <v>42</v>
-      </c>
-      <c r="BE106" s="1">
-        <v>27</v>
-      </c>
-      <c r="BF106" s="1">
-        <v>134</v>
-      </c>
-      <c r="BG106" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="BH106" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="BI106" s="1">
-        <v>0.91</v>
-      </c>
-      <c r="BJ106" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
+      <c r="Z106" s="1"/>
+      <c r="AA106" s="1"/>
+      <c r="AB106" s="1"/>
+      <c r="AC106" s="1"/>
+      <c r="AD106" s="1"/>
+      <c r="AE106" s="1"/>
+      <c r="AF106" s="1"/>
+      <c r="AG106" s="1"/>
+      <c r="AH106" s="1"/>
+      <c r="AI106" s="1"/>
+      <c r="AJ106" s="1"/>
+      <c r="AK106" s="1"/>
+      <c r="AL106" s="1"/>
+      <c r="AM106" s="1"/>
+      <c r="AN106" s="1"/>
+      <c r="AO106" s="1"/>
+      <c r="AP106" s="1"/>
+      <c r="AQ106" s="1"/>
+      <c r="AR106" s="1"/>
+      <c r="AS106" s="1"/>
+      <c r="AT106" s="1"/>
+      <c r="AU106" s="1"/>
+      <c r="AV106" s="1"/>
+      <c r="AW106" s="1"/>
+      <c r="AX106" s="1"/>
+      <c r="AY106" s="1"/>
+      <c r="AZ106" s="1"/>
+      <c r="BA106" s="1"/>
+      <c r="BB106" s="1"/>
+      <c r="BC106" s="1"/>
+      <c r="BD106" s="1"/>
+      <c r="BE106" s="1"/>
+      <c r="BF106" s="1"/>
+      <c r="BG106" s="1"/>
+      <c r="BH106" s="1"/>
+      <c r="BI106" s="1"/>
+      <c r="BJ106" s="1"/>
       <c r="BK106" s="1"/>
-      <c r="BL106" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="BM106" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="BL106" s="1"/>
+      <c r="BM106" s="1"/>
       <c r="BN106" s="1"/>
-      <c r="BO106" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="BP106" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="BQ106" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="BR106" s="1" t="s">
-        <v>299</v>
-      </c>
+      <c r="BO106" s="1"/>
+      <c r="BP106" s="1"/>
+      <c r="BQ106" s="1"/>
+      <c r="BR106" s="1"/>
       <c r="BS106" s="1"/>
-      <c r="BT106" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="BU106" s="2" t="s">
-        <v>495</v>
-      </c>
+      <c r="BT106" s="1"/>
+      <c r="BU106" s="2"/>
     </row>
     <row r="107" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
@@ -52763,89 +53320,8 @@
       <c r="BT498" s="1"/>
       <c r="BU498" s="2"/>
     </row>
-    <row r="499" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A499" s="1"/>
-      <c r="B499" s="2"/>
-      <c r="C499" s="1"/>
-      <c r="D499" s="1"/>
-      <c r="E499" s="1"/>
-      <c r="F499" s="1"/>
-      <c r="G499" s="1"/>
-      <c r="H499" s="1"/>
-      <c r="I499" s="1"/>
-      <c r="J499" s="1"/>
-      <c r="K499" s="1"/>
-      <c r="L499" s="1"/>
-      <c r="M499" s="1"/>
-      <c r="N499" s="1"/>
-      <c r="O499" s="1"/>
-      <c r="P499" s="1"/>
-      <c r="Q499" s="1"/>
-      <c r="R499" s="1"/>
-      <c r="S499" s="1"/>
-      <c r="T499" s="1"/>
-      <c r="U499" s="1"/>
-      <c r="V499" s="1"/>
-      <c r="W499" s="1"/>
-      <c r="X499" s="1"/>
-      <c r="Y499" s="1"/>
-      <c r="Z499" s="1"/>
-      <c r="AA499" s="1"/>
-      <c r="AB499" s="1"/>
-      <c r="AC499" s="1"/>
-      <c r="AD499" s="1"/>
-      <c r="AE499" s="1"/>
-      <c r="AF499" s="1"/>
-      <c r="AG499" s="1"/>
-      <c r="AH499" s="1"/>
-      <c r="AI499" s="1"/>
-      <c r="AJ499" s="1"/>
-      <c r="AK499" s="1"/>
-      <c r="AL499" s="1"/>
-      <c r="AM499" s="1"/>
-      <c r="AN499" s="1"/>
-      <c r="AO499" s="1"/>
-      <c r="AP499" s="1"/>
-      <c r="AQ499" s="1"/>
-      <c r="AR499" s="1"/>
-      <c r="AS499" s="1"/>
-      <c r="AT499" s="1"/>
-      <c r="AU499" s="1"/>
-      <c r="AV499" s="1"/>
-      <c r="AW499" s="1"/>
-      <c r="AX499" s="1"/>
-      <c r="AY499" s="1"/>
-      <c r="AZ499" s="1"/>
-      <c r="BA499" s="1"/>
-      <c r="BB499" s="1"/>
-      <c r="BC499" s="1"/>
-      <c r="BD499" s="1"/>
-      <c r="BE499" s="1"/>
-      <c r="BF499" s="1"/>
-      <c r="BG499" s="1"/>
-      <c r="BH499" s="1"/>
-      <c r="BI499" s="1"/>
-      <c r="BJ499" s="1"/>
-      <c r="BK499" s="1"/>
-      <c r="BL499" s="1"/>
-      <c r="BM499" s="1"/>
-      <c r="BN499" s="1"/>
-      <c r="BO499" s="1"/>
-      <c r="BP499" s="1"/>
-      <c r="BQ499" s="1"/>
-      <c r="BR499" s="1"/>
-      <c r="BS499" s="1"/>
-      <c r="BT499" s="1"/>
-      <c r="BU499" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:BU106" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="71">
-      <filters>
-        <filter val="Survivor"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:BU105" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
